--- a/src/main/resources/excel/Time Expressions Used.xlsx
+++ b/src/main/resources/excel/Time Expressions Used.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1 Tiem Expression" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="2 Time Expression" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="3 Time Expression" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="539">
   <si>
     <t xml:space="preserve">Now</t>
   </si>
@@ -768,6 +769,876 @@
   </si>
   <si>
     <t xml:space="preserve">ɪn ə flæʃ ʌv ˌɪnspəˈreɪʃən</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un día</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə deɪ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">una semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə wik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə mʌnθ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə jɪr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">əˈɡoʊ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pɜr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">during</t>
+  </si>
+  <si>
+    <t xml:space="preserve">durante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">siguiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nɛkst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">last</t>
+  </si>
+  <si>
+    <t xml:space="preserve">último</t>
+  </si>
+  <si>
+    <t xml:space="preserve">læst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">víspera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un día antes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deɪ bɪˈfɔr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yesterday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tomorrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mañana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tomorrow morning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mañana por la mañana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">təˈmɑˌroʊ ˈmɔrnɪŋ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tomorrow afternoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mañana en la tarde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">təˈmɑˌroʊ ˌæftərˈnun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tomorrow night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mañana por la noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">təˈmɑˌroʊ naɪt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day after tomorrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasado mañana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deɪ ˈæftər təˈmɑˌroʊ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a week from today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dentro de una semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə wik frʌm təˈdeɪ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two weeks from tomorrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dos semanas a partir de mañana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tu wiks frʌm təˈmɑˌroʊ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">within one week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wɪˈðɪn wʌn wik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At what time are they coming?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿A qué hora vienen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt wɑt taɪm ɑr ðeɪ ˈkʌmɪŋ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un segundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə ˈsɛkənd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a minute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un minuto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə ˈmɪnət</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a quarter of an hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un cuarto de hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə ˈkwɔrtər ʌv ən ˈaʊər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">an hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">una hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ən ˈaʊər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a half hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə hæf ˈaʊər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in the morning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por la mañana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in the afternoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por la tarde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in the evening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at what time?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿A qué hora?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt wɑt taɪm?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at exactly nine o'clock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exactamente a las nueve en punto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt ɪɡˈzæktli naɪn əˈklɑk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at about two o'clock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alrededor de las dos en punto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">æt əˈbaʊt tu əˈklɑk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in an hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dentro de una hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪn ən ˈaʊər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in a while</t>
+  </si>
+  <si>
+    <t xml:space="preserve">en un momento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">until ten o'clock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasta las diez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ənˈtɪl tɛn əˈklɑk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">before nine o'clock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">antes de las nueve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bɪˈfɔr naɪn əˈklɑk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">after seven o'clock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">después de las siete en punto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈæftər ˈsɛvən əˈklɑk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">since what Time?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desde que hora?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sɪns wɑt taɪm?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">since eight o'clock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desde las ocho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sɪns eɪt əˈklɑk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one hour ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hace una hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wʌn ˈaʊər əˈɡoʊ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">early</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temprano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈɜrli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">late</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tarde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leɪt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What time is it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué hora es?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wɑt taɪm ɪz ɪt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could you tell me the time, please?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Podría decirme la hora, por favor?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kʊd ju tɛl mi ðə taɪm, pliz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you have the time?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Tiene la hora?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">du ju hæv ðə taɪm?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can you tell me what time it is?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Puede decirme qué hora es?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kæn ju tɛl mi wɑt taɪm ɪt ɪz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's one o'clock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es la una.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts wʌn əˈklɑk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's three o'clock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las tres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts θri əˈklɑk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's half past one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es la una y media. (1:30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts hæf pæst wʌn. (1:30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's half past four.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las cuatro y media. (4:30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts hæf pæst fɔr. (4:30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's quarter past two.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las dos y cuarto. (2:15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈkwɔrtər pæst tu. (2:15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's quarter past five.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las cinco y cuarto. (5:15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈkwɔrtər pæst faɪv. (5:15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's quarter to three.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las tres menos cuarto. (2:45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈkwɔrtər tu θri. (2:45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's quarter to six.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las seis menos cuarto. (5:45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈkwɔrtər tu sɪks. (5:45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's ten minutes past seven.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las siete y diez. (7:10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts tɛn ˈmɪnəts pæst ˈsɛvən. (7:10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's twenty minutes past eight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las ocho y veinte. (8:20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈtwɛnti ˈmɪnəts pæst eɪt. (8:20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's twenty minutes to nine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las nueve menos veinte. (8:40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts ˈtwɛnti ˈmɪnəts tu naɪn. (8:40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It's five minutes to ten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son las diez menos cinco. (9:55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɪts faɪv ˈmɪnəts tu tɛn. (9:55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please move the folder to the top right corner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por favor, mueva la carpeta a la esquina superior derecha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pliz muv ðə ˈfoʊldər tu ðə tɑp raɪt ˈkɔrnər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At: Se usa para horas específicas (at 5 o'clock), períodos festivos (at Christmas), y otras expresiones de tiempo (at night). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">We start work at 8 AM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empezamos a trabajar a las 8 AM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The stars shine brightly at night.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las estrellas brillan intensamente por la noche.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They always have a family gathering at Christmas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siempre tienen una reunión familiar en Navidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meet me at the entrance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encuéntrame en la entrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'll call you at lunchtime.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te llamaré a la hora del almuerzo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On: Se utiliza con días y fechas (on Monday, on April 21st). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I will see you on Monday.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te veré el lunes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Her birthday is on July 4th.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su cumpleaños es el 4 de julio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We go out to eat on weekends.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salimos a comer los fines de semana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They are getting married on Valentine's Day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se casarán en el Día de San Valentín.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The meeting is on the first day of spring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La reunión es el primer día de primavera.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In: Se aplica para meses (in July), años (in 1998), estaciones del año (in summer), y partes del día (in the morning), excepto por "at night" como mencioné antes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">She was born in 1995.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella nació en 1995.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It rains a lot in April.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llueve mucho en abril.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We like to travel in summer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nos gusta viajar en verano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He finished the task in an hour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él terminó la tarea en una hora.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They moved here in the 1980s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se mudaron aquí en los años ochenta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before: Indica un momento anterior a otro (before noon). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finish your homework before dinner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termina tu tarea antes de la cena.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She always drinks coffee before leaving the house.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella siempre toma café antes de salir de casa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He turned off the lights before he left.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él apagó las luces antes de irse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They had heard the news before it was officially announced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habían escuchado las noticias antes de que se anunciara oficialmente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We must arrive before the show starts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debemos llegar antes de que comience el espectáculo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After: Se utiliza para indicar un momento posterior a otro (after school). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let's go for a walk after lunch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vamos a dar un paseo después del almuerzo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She cleaned the house after the party.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella limpió la casa después de la fiesta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He went home after the meeting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él fue a casa después de la reunión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They went to the gym after work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fueron al gimnasio después del trabajo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I usually read after putting the kids to bed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suelo leer después de acostar a los niños.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By: Señala un límite de tiempo, un momento en el que algo debe estar terminado (by tomorrow). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please complete the report by Thursday.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por favor completa el informe para el jueves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She promised to send the email by noon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometió enviar el correo electrónico antes del mediodía.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They hope to have finished the construction by September.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esperan haber terminado la construcción para septiembre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He needs to decide by tomorrow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necesita decidir para mañana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The score was tied by halftime.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El marcador estaba empatado para el medio tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During: Usada para señalar que algo ocurre dentro del periodo de tiempo de otro evento (during the movie). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You cannot talk during the exam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No puedes hablar durante el examen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Many shops close during national holidays.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muchas tiendas cierran durante los días festivos nacionales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The phone rang several times during dinner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El teléfono sonó varias veces durante la cena.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He learned French during his stay in France.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprendió francés durante su estancia en Francia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There was a power outage during the storm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hubo un corte de energía durante la tormenta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Until: Indica la continuación de una actividad hasta un punto en el tiempo (until midnight). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work until you finish.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trabaja hasta que termines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The store is open until midnight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La tienda está abierta hasta la medianoche.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They played games until everyone was tired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jugaron juegos hasta que todos estuvieron cansados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep stirring until the mixture thickens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigue revolviendo hasta que la mezcla se espese.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I can't wait until the weekend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No puedo esperar hasta el fin de semana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since: Expresa el inicio de un periodo de tiempo que continúa hasta el presente (since 2010). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I haven't seen him since last year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No lo he visto desde el año pasado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">She has been working here since 2012.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ella ha estado trabajando aquí desde 2012.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They have lived in this town since they were children.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Han vivido en este pueblo desde que eran niños.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We've been waiting here since 3 PM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemos estado esperando aquí desde las 3 PM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He has changed a lot since his accident.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él ha cambiado mucho desde su accidente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For: Se usa para hablar de la duración de una acción (for two hours) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I've been studying Spanish for two years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He estado estudiando español durante dos años.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They rented the apartment for three months.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alquilaron el apartamento durante tres meses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He's going abroad for a week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Él va al extranjero por una semana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We've known each other for a long time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nos conocemos desde hace mucho tiempo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I need to borrow your charger for a day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necesito tomar prestado tu cargador por un día.</t>
   </si>
 </sst>
 </file>
@@ -842,7 +1713,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -851,8 +1722,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2200,4 +3083,1669 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I121"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="47.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="65.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="85.7"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1" s="0"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="0"/>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" s="0"/>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="0"/>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E5" s="0"/>
+      <c r="F5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="0"/>
+      <c r="F6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E7" s="0"/>
+      <c r="F7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="0"/>
+      <c r="F8" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="0"/>
+      <c r="F9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E10" s="0"/>
+      <c r="F10" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E11" s="0"/>
+      <c r="F11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E12" s="0"/>
+      <c r="F12" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="0"/>
+      <c r="F13" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="0"/>
+      <c r="F14" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="0"/>
+      <c r="F15" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E16" s="0"/>
+      <c r="F16" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E17" s="0"/>
+      <c r="F17" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E18" s="0"/>
+      <c r="F18" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E19" s="0"/>
+      <c r="F19" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" s="0"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E21" s="0"/>
+      <c r="F21" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E22" s="0"/>
+      <c r="F22" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E23" s="0"/>
+      <c r="F23" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E24" s="0"/>
+      <c r="F24" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E25" s="0"/>
+      <c r="F25" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E26" s="0"/>
+      <c r="F26" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E27" s="0"/>
+      <c r="F27" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E28" s="0"/>
+      <c r="F28" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="0"/>
+      <c r="F29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="0"/>
+      <c r="F30" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="0"/>
+      <c r="F31" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E32" s="0"/>
+      <c r="F32" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E33" s="0"/>
+      <c r="F33" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E34" s="0"/>
+      <c r="F34" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E35" s="0"/>
+      <c r="F35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="0"/>
+      <c r="F36" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E37" s="0"/>
+      <c r="F37" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E38" s="0"/>
+      <c r="F38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E39" s="0"/>
+      <c r="F39" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E40" s="0"/>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E41" s="0"/>
+      <c r="F41" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E42" s="0"/>
+      <c r="F42" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E43" s="0"/>
+      <c r="F43" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E44" s="0"/>
+      <c r="F44" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E45" s="0"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E46" s="0"/>
+      <c r="F46" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E47" s="0"/>
+      <c r="F47" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E48" s="0"/>
+      <c r="F48" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E49" s="0"/>
+      <c r="F49" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E50" s="0"/>
+      <c r="F50" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E51" s="0"/>
+      <c r="F51" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E52" s="0"/>
+      <c r="F52" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E53" s="0"/>
+      <c r="F53" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E54" s="0"/>
+      <c r="F54" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E55" s="0"/>
+      <c r="F55" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E56" s="0"/>
+      <c r="F56" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E57" s="0"/>
+      <c r="F57" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E58" s="0"/>
+      <c r="F58" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E59" s="0"/>
+      <c r="F59" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E60" s="0"/>
+      <c r="F60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E61" s="0"/>
+      <c r="F61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F68" s="1"/>
+      <c r="I68" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F74" s="1"/>
+      <c r="I74" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" s="3"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I78" s="3"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I79" s="3"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" s="1"/>
+      <c r="I80" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I82" s="3"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I84" s="3"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I85" s="3"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F86" s="1"/>
+      <c r="I86" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I87" s="3"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I88" s="3"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I90" s="3"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="F92" s="1"/>
+      <c r="I92" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I93" s="3"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I95" s="3"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I97" s="3"/>
+    </row>
+    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F98" s="1"/>
+      <c r="I98" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I99" s="3"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I103" s="3"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F104" s="1"/>
+      <c r="I104" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I105" s="3"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I106" s="3"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I107" s="3"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I108" s="3"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I109" s="3"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F110" s="1"/>
+      <c r="I110" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I111" s="3"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I112" s="3"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I113" s="3"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I114" s="3"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I115" s="3"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F116" s="1"/>
+      <c r="I116" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I117" s="3"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I118" s="3"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>